--- a/output/RAW_DATA.xlsx
+++ b/output/RAW_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackw\Desktop\SPUploader\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80D777F-0929-4CC6-B7C3-7B916BC6EA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A01A90A-7023-4DDB-9B7E-5F3AEC1AB73A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5830" yWindow="5130" windowWidth="28800" windowHeight="15370" xr2:uid="{9C448964-F196-46F9-A125-560E7D5DD054}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{9C448964-F196-46F9-A125-560E7D5DD054}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>Old Hostname</t>
   </si>
@@ -195,6 +195,15 @@
   </si>
   <si>
     <t>Laptop assigned to IT</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Incomplete</t>
   </si>
 </sst>
 </file>
@@ -569,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8ED8201-5942-4421-995D-D84CACF90F81}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
@@ -578,7 +587,7 @@
     <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -594,8 +603,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -611,8 +623,11 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="F2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -628,8 +643,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -645,8 +663,11 @@
       <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F4" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -662,8 +683,11 @@
       <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F5" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -679,8 +703,11 @@
       <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="F6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -696,8 +723,11 @@
       <c r="E7" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F7" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
@@ -713,8 +743,11 @@
       <c r="E8" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="F8" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -730,8 +763,11 @@
       <c r="E9" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F9" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -747,8 +783,11 @@
       <c r="E10" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>48</v>
       </c>
@@ -763,6 +802,9 @@
       </c>
       <c r="E11" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
